--- a/fixtures/styles-showcase.xlsx
+++ b/fixtures/styles-showcase.xlsx
@@ -8,7 +8,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
   <si>
     <t>Section</t>
   </si>
@@ -80,6 +80,30 @@
   </si>
   <si>
     <t>coloured</t>
+  </si>
+  <si>
+    <t>Wrap</t>
+  </si>
+  <si>
+    <t>This sentence is far too long for one cell and must wrap onto several lines.</t>
+  </si>
+  <si>
+    <t>middle</t>
+  </si>
+  <si>
+    <t>Overflow</t>
+  </si>
+  <si>
+    <t>This long text spills across the empty neighbours to its right</t>
+  </si>
+  <si>
+    <t>Truncate</t>
+  </si>
+  <si>
+    <t>This long text is cut because the next cell is occupied</t>
+  </si>
+  <si>
+    <t>blocked</t>
   </si>
   <si>
     <t>Format</t>
@@ -306,7 +330,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -342,13 +366,25 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="bottom"/>
+    </xf>
   </cellXfs>
 </styleSheet>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D25"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="4" width="18" customWidth="1"/>
@@ -457,7 +493,7 @@
     </row>
     <row r="19">
       <c r="A19" s="17" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="B19" s="24">
         <v>0.25</v>
@@ -467,6 +503,39 @@
       </c>
       <c r="D19" s="26">
         <v>1234.5</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="B21" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="C21" s="28" t="s">
+        <v>14</v>
+      </c>
+      <c r="D21" s="29" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="B23" s="0" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="17" t="s">
+        <v>29</v>
+      </c>
+      <c r="B25" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="C25" s="0" t="s">
+        <v>31</v>
       </c>
     </row>
   </sheetData>

--- a/fixtures/styles-showcase.xlsx
+++ b/fixtures/styles-showcase.xlsx
@@ -8,7 +8,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
   <si>
     <t>Section</t>
   </si>
@@ -104,6 +104,21 @@
   </si>
   <si>
     <t>blocked</t>
+  </si>
+  <si>
+    <t>Rotation</t>
+  </si>
+  <si>
+    <t>45 up</t>
+  </si>
+  <si>
+    <t>90 up</t>
+  </si>
+  <si>
+    <t>45 down</t>
+  </si>
+  <si>
+    <t>stacked</t>
   </si>
   <si>
     <t>Format</t>
@@ -330,7 +345,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -350,6 +365,18 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="45"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="135"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="255"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyNumberFormat="1"/>
@@ -384,7 +411,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D25"/>
+  <dimension ref="A1:D28"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="4" width="18" customWidth="1"/>
@@ -405,7 +432,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="17" t="s">
+      <c r="A3" s="21" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="2"/>
@@ -413,7 +440,7 @@
       <c r="D3" s="4"/>
     </row>
     <row r="5">
-      <c r="A5" s="17" t="s">
+      <c r="A5" s="21" t="s">
         <v>3</v>
       </c>
       <c r="B5" s="5" t="s">
@@ -462,65 +489,65 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="17" t="s">
+      <c r="A15" s="21" t="s">
         <v>16</v>
       </c>
-      <c r="B15" s="17" t="s">
+      <c r="B15" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="C15" s="18" t="s">
+      <c r="C15" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="D15" s="19" t="s">
+      <c r="D15" s="23" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="20" t="s">
+      <c r="B16" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="C16" s="21" t="s">
+      <c r="C16" s="25" t="s">
         <v>21</v>
       </c>
-      <c r="D16" s="22" t="s">
+      <c r="D16" s="26" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="17">
-      <c r="B17" s="23" t="s">
+      <c r="B17" s="27" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="17" t="s">
-        <v>32</v>
-      </c>
-      <c r="B19" s="24">
+      <c r="A19" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="B19" s="28">
         <v>0.25</v>
       </c>
-      <c r="C19" s="25">
+      <c r="C19" s="29">
         <v>0.25</v>
       </c>
-      <c r="D19" s="26">
+      <c r="D19" s="30">
         <v>1234.5</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="17" t="s">
+      <c r="A21" s="21" t="s">
         <v>24</v>
       </c>
-      <c r="B21" s="27" t="s">
+      <c r="B21" s="31" t="s">
         <v>25</v>
       </c>
-      <c r="C21" s="28" t="s">
+      <c r="C21" s="32" t="s">
         <v>14</v>
       </c>
-      <c r="D21" s="29" t="s">
+      <c r="D21" s="33" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="17" t="s">
+      <c r="A23" s="21" t="s">
         <v>27</v>
       </c>
       <c r="B23" s="0" t="s">
@@ -528,7 +555,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="17" t="s">
+      <c r="A25" s="21" t="s">
         <v>29</v>
       </c>
       <c r="B25" s="0" t="s">
@@ -536,6 +563,25 @@
       </c>
       <c r="C25" s="0" t="s">
         <v>31</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="B27" s="17" t="s">
+        <v>33</v>
+      </c>
+      <c r="C27" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="D27" s="19" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" s="20" t="s">
+        <v>36</v>
       </c>
     </row>
   </sheetData>
